--- a/research/llm_as_a_judge.xlsx
+++ b/research/llm_as_a_judge.xlsx
@@ -448,10 +448,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.09999999999999998</v>
       </c>
     </row>
     <row r="3">
@@ -569,7 +569,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>political_science_international_relations_analyst</t>
+          <t>media_journalism_and_cultural_studies_expert</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -585,7 +585,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>social_media_and_marketing_strategist</t>
+          <t>political_science_international_relations_analyst</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -601,7 +601,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>digital_marketing_and_media_strategy</t>
+          <t>social_media_and_marketing_strategist</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -617,7 +617,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>data_driven_policy_analyst</t>
+          <t>digital_marketing_and_media_strategy</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -633,7 +633,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cultural_humanities_researcher_media_studies</t>
+          <t>data_driven_policy_analyst</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -649,7 +649,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>media_journalism_and_cultural_studies_expert</t>
+          <t>cultural_humanities_researcher_media_studies</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -681,17 +681,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>literary_and_cultural_analyst_cross_cultural</t>
+          <t>multidisciplinary_tech_and_language_developer</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.9</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09999999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -729,23 +729,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>multidisciplinary_tech_and_language_developer</t>
+          <t>strategic_consultant_and_market_analyst</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0.8</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>strategic_consultant_and_market_analyst</t>
+          <t>multilingual_nlp_and_ai_specialist</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -761,33 +761,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>multilingual_nlp_and_ai_specialist</t>
+          <t>legal_policy_and_ethics_researcher</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0.8</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2</v>
+        <v>-0.1000000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>legal_policy_and_ethics_researcher</t>
+          <t>literary_and_cultural_analyst_cross_cultural</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0.8</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1000000000000001</v>
+        <v>0.09999999999999998</v>
       </c>
     </row>
     <row r="24">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C24" t="n">
         <v>0.8</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -841,7 +841,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>digital_platform_developer_and_educator</t>
+          <t>ai_and_nlp_developer</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -857,33 +857,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ai_and_nlp_developer</t>
+          <t>educational_psychologist_and_methodologist</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0.6</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2000000000000001</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>educational_psychologist_and_methodologist</t>
+          <t>digital_platform_developer_and_educator</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.09999999999999998</v>
+        <v>0.2000000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -912,10 +912,10 @@
         <v>0.3</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32">
